--- a/Plan/Table/LiveData/04.CardAddData.xlsx
+++ b/Plan/Table/LiveData/04.CardAddData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FC02593-0E5A-4C47-94A0-028E05CF1C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93F1A25F-AD3D-44FE-BD3C-D59C90B599BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="14505" windowHeight="13485" xr2:uid="{7B87656A-8C4C-4BEF-B715-9BA584F8CD19}"/>
+    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{2146EB23-F7A9-438F-B6D0-1CB477FC5066}"/>
   </bookViews>
   <sheets>
     <sheet name="04.CardAddData" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -451,7 +454,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF896EE-1B7F-4D65-92F2-0EE7CE08CDBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966B9262-206D-4BAD-A9A7-A5FD0588A580}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Plan/Table/LiveData/04.CardAddData.xlsx
+++ b/Plan/Table/LiveData/04.CardAddData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93F1A25F-AD3D-44FE-BD3C-D59C90B599BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAA6A51C-BFAE-4891-9391-28AEE39E84CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{2146EB23-F7A9-438F-B6D0-1CB477FC5066}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{84CF54AC-B866-41F9-93CD-3683A9AD63BE}"/>
   </bookViews>
   <sheets>
     <sheet name="04.CardAddData" sheetId="1" r:id="rId1"/>
@@ -454,9 +454,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966B9262-206D-4BAD-A9A7-A5FD0588A580}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CCBE576-2D5D-4E3A-BCD8-C251641A3ED7}">
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1226,6 +1225,41 @@
         <v>0</v>
       </c>
       <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>123</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>0</v>
       </c>
     </row>

--- a/Plan/Table/LiveData/04.CardAddData.xlsx
+++ b/Plan/Table/LiveData/04.CardAddData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAA6A51C-BFAE-4891-9391-28AEE39E84CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2A05678-13E2-4918-8B90-AD9D591A6342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{84CF54AC-B866-41F9-93CD-3683A9AD63BE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{222E6FB1-09F6-4C81-8D28-312B4FD7B813}"/>
   </bookViews>
   <sheets>
     <sheet name="04.CardAddData" sheetId="1" r:id="rId1"/>
@@ -454,8 +454,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CCBE576-2D5D-4E3A-BCD8-C251641A3ED7}">
-  <dimension ref="A1:K23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{483FC17C-4E42-4E86-8FF3-A8BBC9E8E416}">
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1260,6 +1260,41 @@
         <v>0</v>
       </c>
       <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>124</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
         <v>0</v>
       </c>
     </row>

--- a/Plan/Table/LiveData/04.CardAddData.xlsx
+++ b/Plan/Table/LiveData/04.CardAddData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2A05678-13E2-4918-8B90-AD9D591A6342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07C6080A-75AC-407E-B5D8-970145979627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{222E6FB1-09F6-4C81-8D28-312B4FD7B813}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="9405" windowHeight="15585" xr2:uid="{F51990D0-AD64-4026-8722-28F2C84F121D}"/>
   </bookViews>
   <sheets>
     <sheet name="04.CardAddData" sheetId="1" r:id="rId1"/>
@@ -39,11 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>설명</t>
+  </si>
+  <si>
     <t>Value_1</t>
   </si>
   <si>
@@ -71,7 +74,37 @@
     <t>Value_9</t>
   </si>
   <si>
-    <t>Value_10</t>
+    <t>랜덤 일반 타일 (Value_1)회 타격</t>
+  </si>
+  <si>
+    <t>도움 타일 타격 시 골드 획득</t>
+  </si>
+  <si>
+    <t>방해 타일 타격 시 골드 획득</t>
+  </si>
+  <si>
+    <t>균열 타일 파괴 시 골드 획득</t>
+  </si>
+  <si>
+    <t>도움 타일 파괴 시 골드 획득</t>
+  </si>
+  <si>
+    <t>방해 타일 파괴 시 골드 획득</t>
+  </si>
+  <si>
+    <t>타일 (value_1) 파괴 시 타격된 모든 타일 파괴</t>
+  </si>
+  <si>
+    <t>타일 n(value_1) 파괴 시 특정 태그(value_2) 카드 m(value_3)장 드로우</t>
+  </si>
+  <si>
+    <t>타일 n(value_1) 파괴 시 특정 방향(value_2) 일반 타일 전체 파괴</t>
+  </si>
+  <si>
+    <t>특정 방해 타일 타격 가능</t>
+  </si>
+  <si>
+    <t>타격 지점 균열 부여</t>
   </si>
 </sst>
 </file>
@@ -454,8 +487,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{483FC17C-4E42-4E86-8FF3-A8BBC9E8E416}">
-  <dimension ref="A1:K24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C5097D-4694-4018-A5EF-FB40E5F30863}">
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -497,14 +530,14 @@
       <c r="A2">
         <v>101</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>3300</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -532,14 +565,14 @@
       <c r="A3">
         <v>102</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>5000</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -567,11 +600,11 @@
       <c r="A4">
         <v>103</v>
       </c>
-      <c r="B4">
-        <v>10000</v>
+      <c r="B4" t="s">
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -602,14 +635,14 @@
       <c r="A5">
         <v>104</v>
       </c>
-      <c r="B5">
-        <v>10000</v>
+      <c r="B5" t="s">
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -637,14 +670,14 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="B6" t="s">
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -672,14 +705,14 @@
       <c r="A7">
         <v>106</v>
       </c>
-      <c r="B7">
-        <v>7</v>
+      <c r="B7" t="s">
+        <v>15</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -707,14 +740,14 @@
       <c r="A8">
         <v>107</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
         <v>2</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
       <c r="D8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -742,11 +775,11 @@
       <c r="A9">
         <v>108</v>
       </c>
-      <c r="B9">
-        <v>2</v>
+      <c r="B9" t="s">
+        <v>17</v>
       </c>
       <c r="C9">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -777,17 +810,17 @@
       <c r="A10">
         <v>109</v>
       </c>
-      <c r="B10">
-        <v>4</v>
+      <c r="B10" t="s">
+        <v>18</v>
       </c>
       <c r="C10">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -812,14 +845,14 @@
       <c r="A11">
         <v>110</v>
       </c>
-      <c r="B11">
-        <v>3</v>
+      <c r="B11" t="s">
+        <v>19</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -847,11 +880,11 @@
       <c r="A12">
         <v>111</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
         <v>1</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -882,11 +915,11 @@
       <c r="A13">
         <v>112</v>
       </c>
-      <c r="B13">
-        <v>5</v>
+      <c r="B13" t="s">
+        <v>21</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -910,391 +943,6 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>113</v>
-      </c>
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>114</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>115</v>
-      </c>
-      <c r="B16">
-        <v>5</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>116</v>
-      </c>
-      <c r="B17">
-        <v>5000</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>117</v>
-      </c>
-      <c r="B18">
-        <v>1000</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>118</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>119</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>120</v>
-      </c>
-      <c r="B21">
-        <v>10000</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>121</v>
-      </c>
-      <c r="B22">
-        <v>10000</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>123</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>124</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
         <v>0</v>
       </c>
     </row>

--- a/Plan/Table/LiveData/04.CardAddData.xlsx
+++ b/Plan/Table/LiveData/04.CardAddData.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07C6080A-75AC-407E-B5D8-970145979627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E0ADBF6-4297-4D9D-8CA3-7BBDAC61AECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="9405" windowHeight="15585" xr2:uid="{F51990D0-AD64-4026-8722-28F2C84F121D}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="14610" windowHeight="15585" xr2:uid="{094FACE6-8702-47BD-B465-15E59B38EC4A}"/>
   </bookViews>
   <sheets>
     <sheet name="04.CardAddData" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>설명</t>
+    <t>Card_Add_Type</t>
   </si>
   <si>
     <t>Value_1</t>
@@ -74,37 +74,7 @@
     <t>Value_9</t>
   </si>
   <si>
-    <t>랜덤 일반 타일 (Value_1)회 타격</t>
-  </si>
-  <si>
-    <t>도움 타일 타격 시 골드 획득</t>
-  </si>
-  <si>
-    <t>방해 타일 타격 시 골드 획득</t>
-  </si>
-  <si>
-    <t>균열 타일 파괴 시 골드 획득</t>
-  </si>
-  <si>
-    <t>도움 타일 파괴 시 골드 획득</t>
-  </si>
-  <si>
-    <t>방해 타일 파괴 시 골드 획득</t>
-  </si>
-  <si>
-    <t>타일 (value_1) 파괴 시 타격된 모든 타일 파괴</t>
-  </si>
-  <si>
-    <t>타일 n(value_1) 파괴 시 특정 태그(value_2) 카드 m(value_3)장 드로우</t>
-  </si>
-  <si>
-    <t>타일 n(value_1) 파괴 시 특정 방향(value_2) 일반 타일 전체 파괴</t>
-  </si>
-  <si>
-    <t>특정 방해 타일 타격 가능</t>
-  </si>
-  <si>
-    <t>타격 지점 균열 부여</t>
+    <t>Value_10</t>
   </si>
 </sst>
 </file>
@@ -487,11 +457,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C5097D-4694-4018-A5EF-FB40E5F30863}">
-  <dimension ref="A1:K13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AD067A-A0B8-48DA-9697-725D3FEEDD35}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -525,13 +496,16 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>101</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -560,13 +534,16 @@
       <c r="K2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>102</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -595,13 +572,16 @@
       <c r="K3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>103</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
+      <c r="B4">
+        <v>4</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -630,13 +610,16 @@
       <c r="K4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>104</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
+      <c r="B5">
+        <v>5</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -665,13 +648,16 @@
       <c r="K5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
+      <c r="B6">
+        <v>6</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -700,13 +686,16 @@
       <c r="K6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>106</v>
       </c>
-      <c r="B7" t="s">
-        <v>15</v>
+      <c r="B7">
+        <v>7</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -735,13 +724,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>107</v>
       </c>
-      <c r="B8" t="s">
-        <v>16</v>
+      <c r="B8">
+        <v>8</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -770,13 +762,16 @@
       <c r="K8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>108</v>
       </c>
-      <c r="B9" t="s">
-        <v>17</v>
+      <c r="B9">
+        <v>10</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -805,13 +800,16 @@
       <c r="K9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>109</v>
       </c>
-      <c r="B10" t="s">
-        <v>18</v>
+      <c r="B10">
+        <v>11</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -840,13 +838,16 @@
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>110</v>
       </c>
-      <c r="B11" t="s">
-        <v>19</v>
+      <c r="B11">
+        <v>12</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -875,13 +876,16 @@
       <c r="K11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>111</v>
       </c>
-      <c r="B12" t="s">
-        <v>20</v>
+      <c r="B12">
+        <v>13</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -910,13 +914,16 @@
       <c r="K12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>112</v>
       </c>
-      <c r="B13" t="s">
-        <v>21</v>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13">
         <v>10000</v>
@@ -943,6 +950,9 @@
         <v>0</v>
       </c>
       <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>0</v>
       </c>
     </row>
